--- a/cp-card-custodian/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-card-custodian/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T15:58:57+00:00</t>
+    <t>2026-05-05T16:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-card-custodian/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-card-custodian/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T16:17:29+00:00</t>
+    <t>2026-05-06T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -991,7 +991,7 @@
 </t>
   </si>
   <si>
-    <t>Organization which maintains the document</t>
+    <t>Organisme responsable de la gestion du document. Information transmise dans le VIHF.</t>
   </si>
   <si>
     <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>

--- a/cp-card-custodian/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-card-custodian/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T12:21:18+00:00</t>
+    <t>2026-05-27T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -991,7 +991,7 @@
 </t>
   </si>
   <si>
-    <t>Organisme responsable de la gestion du document. Information transmise dans le VIHF.</t>
+    <t>Organisme responsable de la gestion du document. Dans le cadre XDS, il s'agit d'une information transmise dans le VIHF.</t>
   </si>
   <si>
     <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>

--- a/cp-card-custodian/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-card-custodian/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:29:51+00:00</t>
+    <t>2026-05-28T14:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -994,7 +994,7 @@
     <t>Organisme responsable de la gestion du document. Dans le cadre XDS, il s'agit d'une information transmise dans le VIHF.</t>
   </si>
   <si>
-    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
+    <t>Correspond à l’organisation responsable de la conservation, de la maintenance et/ou de l’accès au document, et non nécessairement à l’auteur ou à l’hébergeur technique.</t>
   </si>
   <si>
     <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
